--- a/ky/downloads/data-excel/9.5.2.xlsx
+++ b/ky/downloads/data-excel/9.5.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B9EE43-8F5A-4916-B3A5-E919934A858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -55,8 +56,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +152,19 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -195,34 +209,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -231,21 +241,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -261,9 +274,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -301,9 +314,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -338,7 +351,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -373,7 +386,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -546,8 +559,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" style="1" customWidth="1"/>
@@ -563,96 +576,100 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:18" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="3"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="2"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>2010</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>2011</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>2012</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>2013</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
         <v>2014</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="10">
         <v>2015</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="10">
         <v>2016</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="10">
         <v>2017</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="11">
         <v>2018</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="11">
         <v>2019</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>2020</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="10">
         <v>2021</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="10">
         <v>2022</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="10">
         <v>2023</v>
       </c>
+      <c r="R4" s="10">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" s="18" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:18" s="15" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="16">
@@ -688,50 +705,29 @@
       <c r="N5" s="17">
         <v>534</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="14">
         <v>515</v>
       </c>
       <c r="P5" s="17">
         <v>605</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="14">
         <v>631</v>
       </c>
+      <c r="R5" s="14">
+        <v>620</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
